--- a/data/trans_orig/IP16A98-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A98-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>9236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26221</t>
+          <t>26085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>33107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29271</t>
+          <t>28562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58003</t>
+          <t>58460</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67644</t>
+          <t>67902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43648</t>
+          <t>43544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>50485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51746</t>
+          <t>51270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60498</t>
+          <t>60496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98483</t>
+          <t>98396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109658</t>
+          <t>109635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20748</t>
+          <t>20782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27810</t>
+          <t>27711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17444</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24984</t>
+          <t>24920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40789</t>
+          <t>41142</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50810</t>
+          <t>51126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>20869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>21582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38290</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46330</t>
+          <t>46314</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31573</t>
+          <t>31501</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>119744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132893</t>
+          <t>132808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122982</t>
+          <t>123054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138009</t>
+          <t>138067</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247444</t>
+          <t>247471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266839</t>
+          <t>267594</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18838</t>
+          <t>19296</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17002</t>
+          <t>17542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38326</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46990</t>
+          <t>46675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22566</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29084</t>
+          <t>29194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37900</t>
+          <t>37955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30971</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38892</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62769</t>
+          <t>63660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75183</t>
+          <t>75122</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19827</t>
+          <t>20745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33488</t>
+          <t>33689</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28538</t>
+          <t>28901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49743</t>
+          <t>48825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60505</t>
+          <t>60072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,35%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>19947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29962</t>
+          <t>29695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>39151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29345</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37240</t>
+          <t>37927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56783</t>
+          <t>58056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98116</t>
+          <t>98020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111758</t>
+          <t>112221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104959</t>
+          <t>104254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193954</t>
+          <t>192681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>213497</t>
+          <t>212810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16409</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21053</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27065</t>
+          <t>27591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34600</t>
+          <t>34656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23625</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35112</t>
+          <t>35124</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43268</t>
+          <t>43352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33733</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43752</t>
+          <t>43491</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71982</t>
+          <t>72149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85460</t>
+          <t>84822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>21060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>23742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32057</t>
+          <t>32403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35169</t>
+          <t>34540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43476</t>
+          <t>43697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61574</t>
+          <t>62260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74134</t>
+          <t>73815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30966</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26205</t>
+          <t>26541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47093</t>
+          <t>45978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46991</t>
+          <t>48056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73758</t>
+          <t>74126</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56043</t>
+          <t>55960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95556</t>
+          <t>96671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128629</t>
+          <t>128749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>49092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>23963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>46435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46865</t>
+          <t>49549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85107</t>
+          <t>86352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127797</t>
+          <t>128623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158059</t>
+          <t>158100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136646</t>
+          <t>135766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157541</t>
+          <t>158238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274809</t>
+          <t>273564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>313051</t>
+          <t>310367</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A98-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A98-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1574</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8760</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5450</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2677</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9699</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2620</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9594</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>15,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4304</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9236</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33494</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29038</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36224</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30334</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26085</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>33107</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>26190</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>33164</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>84,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>33494</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28562</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>35833</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58460</t>
+          <t>57848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67902</t>
+          <t>68128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37798</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37798</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37798</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>35784</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>35784</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>35784</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>37798</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>37798</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>37798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8400</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4847</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13806</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5293</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2554</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9495</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9408</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,98%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8400</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4863</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14089</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56959</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51553</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>60512</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>47746</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43544</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>50485</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>43631</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>51001</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,02%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>56959</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>51270</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>60496</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98396</t>
+          <t>98226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109635</t>
+          <t>110167</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>65359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>65359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>65359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53039</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53039</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53039</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>65359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>65359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>65359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,67 +1413,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>5427</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9526</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>4875</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2159</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9088</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2066</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9005</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5427</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2218</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9478</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>15725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21711</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17612</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24837</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>24995</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20782</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27711</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20865</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>27804</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>69,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21711</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>17660</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>24920</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41142</t>
+          <t>41282</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51126</t>
+          <t>50900</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5344</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2530</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9368</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1854</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5054</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5344</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2679</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9344</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18917</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14893</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21731</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24069</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25340</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20822</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25342</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>18917</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14917</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>21582</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,97%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46314</t>
+          <t>46402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24261</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24261</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24261</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25923</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25923</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>24261</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>24261</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>24261</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16896</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31398</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>17473</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11808</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24872</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11807</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24464</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>8,16%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23475</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>16488</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31501</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>31850</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51700</t>
+          <t>51779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>131080</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>123157</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>137659</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>79,68%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>127143</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>119744</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>132808</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>120152</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>132809</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>87,92%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>82,8%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>83,08%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>91,84%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>131080</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123054</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>138067</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>84,81%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>79,62%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>366</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247471</t>
+          <t>247392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267594</t>
+          <t>267321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>154555</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>154555</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>154555</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>144616</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>144616</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>144616</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>154555</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>154555</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>154555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7607</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4328</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7737</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7799</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3321</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1164</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6434</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20655</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22737</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22705</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19296</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25202</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19234</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25179</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>83,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20655</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17542</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22812</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46675</t>
+          <t>47044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3017,67 +3017,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>7638</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3970</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12337</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>7828</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4284</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13045</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4233</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12612</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7638</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4143</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12569</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35458</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30759</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39126</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>34411</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>29194</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37955</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>29627</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38006</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>81,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35458</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>30527</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>38953</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>82,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63660</t>
+          <t>63704</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75122</t>
+          <t>75172</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4898</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12839</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5587</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2435</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9808</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2643</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10055</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>15,47%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8521</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4545</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12620</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>25,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>19996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24925</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20607</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28548</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>74,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>30537</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26316</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33689</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26069</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>33481</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>84,53%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24925</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20826</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>28901</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>74,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48825</t>
+          <t>49574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60072</t>
+          <t>60849</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9738</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,79%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3925</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1765</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7766</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7387</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5565</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2811</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9806</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,45%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17193</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13020</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19948</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18140</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14299</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20300</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14678</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>20638</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>17193</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>12952</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>19947</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>75,55%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29695</t>
+          <t>30213</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39151</t>
+          <t>39310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -3929,52 +3929,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18186</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33081</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>21668</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15240</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29441</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29092</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>25045</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19022</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>33523</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37927</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58056</t>
+          <t>57146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98231</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>90195</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>105090</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>79,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>105793</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>98020</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>112221</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>98369</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>112688</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>83,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,9%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>98231</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>89753</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>104254</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>192681</t>
+          <t>193591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>212810</t>
+          <t>213308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2541</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5084</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3883</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1779</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7407</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24,29%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14892</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12349</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16361</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12100</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8576</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14204</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>75,71%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31507</t>
+          <t>25616</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27591</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34656</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7532</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4040</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12225</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6768</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3271</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11499</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>21923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33703</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29010</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37195</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>39855</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35124</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>43352</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43491</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>79585</t>
+          <t>67587</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72149</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84822</t>
+          <t>72358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5545</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2508</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8576</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13409</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11629</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32971</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>41463</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,39%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>28575</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23742</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32403</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>76,92%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40223</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34540</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43697</t>
+          <t>33133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>67672</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62260</t>
+          <t>60961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73815</t>
+          <t>73198</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14675</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8529</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26034</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>13517</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3831</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29901</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>17,34%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26541</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28882</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45978</t>
+          <t>35140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47638</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36279</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>53784</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>64440</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>48056</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>74126</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>82,66%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49327</t>
+          <t>41327</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>35537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55960</t>
+          <t>44932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>88965</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96671</t>
+          <t>77153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128749</t>
+          <t>96749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21832</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42758</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>32743</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19615</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>49092</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23963</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46435</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>58105</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49549</t>
+          <t>46288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86352</t>
+          <t>71920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>134659</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122194</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143120</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>86,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>144972</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>128623</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>158100</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>81,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>72,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>148685</t>
+          <t>115180</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135766</t>
+          <t>107536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158238</t>
+          <t>122620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>293657</t>
+          <t>249839</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273564</t>
+          <t>236024</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>310367</t>
+          <t>261656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
